--- a/src/aw-dawid/Analiza wielowymiarowa.xlsx
+++ b/src/aw-dawid/Analiza wielowymiarowa.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="818" documentId="11_1CE57E2DD3C84F39559BD3B788AFFB502B3FCBC8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AB5F99D-4184-4326-97F7-8BAE2A7C1E30}"/>
+  <xr:revisionPtr revIDLastSave="852" documentId="11_1CE57E2DD3C84F39559BD3B788AFFB502B3FCBC8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE6810C-F455-4117-9D65-9B0F608612B4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dane zakodowane" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="147">
   <si>
     <t>x1</t>
   </si>
@@ -275,28 +275,28 @@
     <t>dochody budżetów województw na 1 mieszkanca w roku 2024.</t>
   </si>
   <si>
+    <t>GOSPODARKA</t>
+  </si>
+  <si>
+    <t>jednostki nowo zarejestrowane w rejestrze REGON w roku 2024 na 10 tys. Ludności</t>
+  </si>
+  <si>
+    <t>INWESTYCJE</t>
+  </si>
+  <si>
+    <t>Przeciętne miesięczne wynagrodzenia brutto w 2024</t>
+  </si>
+  <si>
+    <t>INSRASTRUKTURA TRANSPORTOWA</t>
+  </si>
+  <si>
     <t>nakłady inwestycyjne w przedsiębiorstwach na 1 mieszkańca w 2024</t>
   </si>
   <si>
-    <t>jednostki nowo zarejestrowane w rejestrze REGON w roku 2024 na 10 tys. Ludności</t>
-  </si>
-  <si>
-    <t>Stopa % bezrobocia w grudniu 2024</t>
-  </si>
-  <si>
     <t>.</t>
   </si>
   <si>
-    <t>Przeciętne miesięczne wynagrodzenia brutto w 2024</t>
-  </si>
-  <si>
-    <t>WSPÓŁCZYNNIK AKTYWNOŚCI ZAWODOWEJ OSÓB W WIEKU 15-89 LAT w 4 kwartale 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BENEFICJENCI ŚRODOWISKOWEJ POMOCY SPOŁECZNEJ w %</t>
-  </si>
-  <si>
-    <t>Liczba mieszkań na 1000 mieszkańców w 2024 r</t>
+    <t>ZASOBY LUDZKIE</t>
   </si>
   <si>
     <r>
@@ -313,6 +313,9 @@
     </r>
   </si>
   <si>
+    <t>STAN MATERIALNY</t>
+  </si>
+  <si>
     <r>
       <t>Wydatki budzetów gmin I miast na prawach powiatu na kulturę I ochronę dziedzictwa narodowego na 1 mieszkanca</t>
     </r>
@@ -327,6 +330,9 @@
     </r>
   </si>
   <si>
+    <t>DEMOGRAFIA</t>
+  </si>
+  <si>
     <r>
       <t>Wydatki budzetów gmin I miast na prawach powiatu na oświatena 1 mieszkanca</t>
     </r>
@@ -339,6 +345,9 @@
       </rPr>
       <t xml:space="preserve"> w 2024</t>
     </r>
+  </si>
+  <si>
+    <t>OCHRONA ZDROWIA</t>
   </si>
   <si>
     <r>
@@ -364,6 +373,9 @@
     </r>
   </si>
   <si>
+    <t>KULTURA</t>
+  </si>
+  <si>
     <r>
       <t>wydatk</t>
     </r>
@@ -387,10 +399,100 @@
     </r>
   </si>
   <si>
-    <t>miejsca noclegowe na 1000 ludnosci w 2024</t>
-  </si>
-  <si>
-    <t>udzielone noclegi ogółem styczeń-grudzień na 10000 ludności w 2024</t>
+    <t>WARUNKI BYTOWE</t>
+  </si>
+  <si>
+    <t>liczba rowerow publicznych na 1000 ludnosciu 2024</t>
+  </si>
+  <si>
+    <t>TURYSTYKA</t>
+  </si>
+  <si>
+    <t>drogi dla rowerow na 10,000 km2 2024</t>
+  </si>
+  <si>
+    <t>EDUKACJA</t>
+  </si>
+  <si>
+    <t>kilometry drog publiczncyh ogolem - liczba bezwgledna - 2024</t>
+  </si>
+  <si>
+    <t>kilometry drog publiczncyh o nawierzchni twardej - liczba bezwgledna - 2024</t>
+  </si>
+  <si>
+    <t>ogółem (przystanki autobusowe (z trolejbusowymi) i tramwajowe, przystanki wspólne dla tramwajów i autobusów) 2024</t>
+  </si>
+  <si>
+    <t>długość linii komunikacji miejskiej na 1000 mieszkańców 2024</t>
+  </si>
+  <si>
+    <t>przewozy pasażerskie na 1 mieszkańca 2024</t>
+  </si>
+  <si>
+    <t>LINIE REGULARNEJ KOMUNIKACJI AUTOBUSOWEJ  w km w 2024</t>
+  </si>
+  <si>
+    <t>samochody osobowe ogolem 2024</t>
+  </si>
+  <si>
+    <t>linie kolejowe ogółem na 100 km2 w 2024</t>
+  </si>
+  <si>
+    <t>wypadki drogowe ogolem 2024</t>
+  </si>
+  <si>
+    <t>WSPÓŁCZYNNIK AKTYWNOŚCI ZAWODOWEJ OSÓB W WIEKU 15-89 LAT w 4 kwartale 2024</t>
+  </si>
+  <si>
+    <t>odsetek ludnosci w wieku produkcyjnym - 2021 sp</t>
+  </si>
+  <si>
+    <t>odsetek ludnosci z wyksztalceniem wyzszym. 2021 sp</t>
+  </si>
+  <si>
+    <t>Współczynnik obciążenia demograficznego (liczba osób w wieku nieprodukcyjnym na 100 osób w wieku produkcyjnym - 2024</t>
+  </si>
+  <si>
+    <t>Stopa % bezrobocia w grudniu 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BENEFICJENCI ŚRODOWISKOWEJ POMOCY SPOŁECZNEJ w %</t>
+  </si>
+  <si>
+    <t>wskaznik urbanizacji 2021 - spis powszechny - ile osob % mieszka w miastach</t>
+  </si>
+  <si>
+    <t>populacja - spis powszechny 2021</t>
+  </si>
+  <si>
+    <t>gęstość zaludnienie (os / km2) - 2021 SP</t>
+  </si>
+  <si>
+    <t>emigranci - 2021 sp - odsetek emigrantów w % względem ludnosci wojewodztwa - czasowy pobyt za granica</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LUDNOŚĆ PRZYBYŁA DO MIEJSCOWOŚCI AKTUALNEGO ZAMIESZKANIA W LATACH 2011-2021  Z INNEGO MIEJSCA W KRAJU </t>
+  </si>
+  <si>
+    <t>Przyrost naturalny na 1000 ludności. - 2024</t>
+  </si>
+  <si>
+    <t>saldo migracji stałej na 1000 ludnosci - 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lekarze pracujący bezpośrednio z pacjentem według województw w przeliczeniu na 10 tys. Mieszkańców – stan w dniu 31 grudnia 2023</t>
+  </si>
+  <si>
+    <t>Lekarze dentyści pracujący bezpośrednio z pacjentem według województw – na 10 tys Mieszkańców – stan 31 grudnia 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pielęgniarki pracujące bezpośrednio z pacjentem według województw na 10 tys mieszkańców – 31 grudnia 2023</t>
+  </si>
+  <si>
+    <t>Położne na 10,000 kobiet 31 grudnia 2023</t>
+  </si>
+  <si>
+    <t>łóżka na oddziałach kardiologicznych na 10 tys. ludności</t>
   </si>
   <si>
     <t>biblioteki publiczne na 10 000 ludności w 2024</t>
@@ -408,43 +510,7 @@
     <t>uczestnicy imprez (wydarzeń kulturalnych) organizowanych przez teatry i instytucje muzyczne, muzea, galerie sztuki, kina oraz centra, ośrodki kultury, domy kultury, kluby i świetlice na 1 000 ludności w 2024</t>
   </si>
   <si>
-    <t xml:space="preserve"> Lekarze pracujący bezpośrednio z pacjentem według województw w przeliczeniu na 10 tys. Mieszkańców – stan w dniu 31 grudnia 2023</t>
-  </si>
-  <si>
-    <t>Lekarze dentyści pracujący bezpośrednio z pacjentem według województw – na 10 tys Mieszkańców – stan 31 grudnia 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pielęgniarki pracujące bezpośrednio z pacjentem według województw na 10 tys mieszkańców – 31 grudnia 2023</t>
-  </si>
-  <si>
-    <t>Położne na 10,000 kobiet 31 grudnia 2023</t>
-  </si>
-  <si>
-    <t>łóżka na oddziałach kardiologicznych na 10 tys. ludności</t>
-  </si>
-  <si>
-    <t>dzieci w przedszkolach i innych formach wychowania przedszkolnego na 1 tys. dzieci w wieku 3-5 lat 2024</t>
-  </si>
-  <si>
-    <t>wskaznik urbanizacji 2021 - spis powszechny - ile osob % mieszka w miastach</t>
-  </si>
-  <si>
-    <t>populacja - spis powszechny 2021</t>
-  </si>
-  <si>
-    <t>gęstość zaludnienie (os / km2) - 2021 SP</t>
-  </si>
-  <si>
-    <t>odsetek ludnosci w wieku produkcyjnym - 2021 sp</t>
-  </si>
-  <si>
-    <t>odsetek ludnosci z wyksztalceniem wyzszym. 2021 sp</t>
-  </si>
-  <si>
-    <t>emigranci - 2021 sp - odsetek emigrantów w % względem ludnosci wojewodztwa - czasowy pobyt za granica</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LUDNOŚĆ PRZYBYŁA DO MIEJSCOWOŚCI AKTUALNEGO ZAMIESZKANIA W LATACH 2011-2021  Z INNEGO MIEJSCA W KRAJU </t>
+    <t>Liczba mieszkań na 1000 mieszkańców w 2024 r</t>
   </si>
   <si>
     <r>
@@ -476,67 +542,34 @@
     </r>
   </si>
   <si>
-    <t>Współczynnik obciążenia demograficznego (liczba osób w wieku nieprodukcyjnym na 100 osób w wieku produkcyjnym - 2024</t>
-  </si>
-  <si>
-    <t>Przyrost naturalny na 1000 ludności. - 2024</t>
-  </si>
-  <si>
-    <t>saldo migracji stałej na 1000 ludnosci - 2024</t>
+    <t>liczba miejsc w domach studenckich w stosunku do liczby studentow 2024 - jaki odsetek studentow domy domy studenckie są w stanie pomieścić</t>
+  </si>
+  <si>
+    <t>studenci korzystający z domów studenckich w % ogółu studentów 2024</t>
+  </si>
+  <si>
+    <t>zasoby mieszkaniowe gim komunalne 2024</t>
+  </si>
+  <si>
+    <t>miejsca noclegowe na 1000 ludnosci w 2024</t>
+  </si>
+  <si>
+    <t>udzielone noclegi ogółem styczeń-grudzień na 10000 ludności w 2024</t>
+  </si>
+  <si>
+    <t>zdawalnsoc egzaminow maturalnych - 2024</t>
+  </si>
+  <si>
+    <t>dzieci w przedszkolach i innych formach wychowania przedszkolnego na 1 tys. dzieci w wieku 3-5 lat 2024</t>
   </si>
   <si>
     <t>liczba studentów przypadających na jednego nauczyciela akademickiego - 2024</t>
   </si>
   <si>
-    <t>liczba miejsc w domach studenckich w stosunku do liczby studentow 2024 - jaki odsetek studentow domy domy studenckie są w stanie pomieścić</t>
-  </si>
-  <si>
-    <t>studenci korzystający z domów studenckich w % ogółu studentów 2024</t>
-  </si>
-  <si>
     <t>studencki uczelni na 10,000 ludnosci - 2024</t>
   </si>
   <si>
     <t>studenci w wojewodztwach. liczba calkowita. 2024</t>
-  </si>
-  <si>
-    <t>zdawalnsoc egzaminow maturalnych - 2024</t>
-  </si>
-  <si>
-    <t>liczba rowerow publicznych na 1000 ludnosciu 2024</t>
-  </si>
-  <si>
-    <t>drogi dla rowerow na 10,000 km2 2024</t>
-  </si>
-  <si>
-    <t>kilometry drog publiczncyh ogolem - liczba bezwgledna - 2024</t>
-  </si>
-  <si>
-    <t>kilometry drog publiczncyh o nawierzchni twardej - liczba bezwgledna - 2024</t>
-  </si>
-  <si>
-    <t>ogółem (przystanki autobusowe (z trolejbusowymi) i tramwajowe, przystanki wspólne dla tramwajów i autobusów) 2024</t>
-  </si>
-  <si>
-    <t>długość linii komunikacji miejskiej na 1000 mieszkańców 2024</t>
-  </si>
-  <si>
-    <t>przewozy pasażerskie na 1 mieszkańca 2024</t>
-  </si>
-  <si>
-    <t>LINIE REGULARNEJ KOMUNIKACJI AUTOBUSOWEJ  w km w 2024</t>
-  </si>
-  <si>
-    <t>linie kolejowe ogółem na 100 km2 w 2024</t>
-  </si>
-  <si>
-    <t>samochody osobowe ogolem 2024</t>
-  </si>
-  <si>
-    <t>wypadki drogowe ogolem 2024</t>
-  </si>
-  <si>
-    <t>zasoby mieszkaniowe gim komunalne 2024</t>
   </si>
   <si>
     <t>analizy głównie bez procesu standaryzacji</t>
@@ -668,7 +701,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -679,6 +712,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
         <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -747,7 +786,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -774,14 +813,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Kolumna" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -3978,403 +4016,240 @@
       <c r="AI19" s="5"/>
     </row>
     <row r="20" spans="1:58" ht="12.75" customHeight="1">
-      <c r="AD20" s="22"/>
-      <c r="AE20" s="22"/>
-      <c r="AF20" s="22"/>
-      <c r="AG20" s="22"/>
-      <c r="AH20" s="22"/>
-      <c r="AI20" s="23"/>
-      <c r="AJ20" s="22"/>
-      <c r="AK20" s="22"/>
-      <c r="AL20" s="22"/>
-      <c r="AM20" s="22"/>
+      <c r="AI20" s="22"/>
     </row>
     <row r="21" spans="1:58" ht="12.75" customHeight="1">
-      <c r="AD21" s="22"/>
-      <c r="AE21" s="22"/>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="22"/>
-      <c r="AH21" s="22"/>
-      <c r="AI21" s="24"/>
-      <c r="AJ21" s="22"/>
-      <c r="AK21" s="22"/>
-      <c r="AL21" s="22"/>
-      <c r="AM21" s="22"/>
+      <c r="AI21" s="23"/>
       <c r="AR21" s="4"/>
       <c r="AS21" s="4"/>
     </row>
     <row r="22" spans="1:58" ht="12.75" customHeight="1">
       <c r="B22" s="3"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="25"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="25"/>
-      <c r="AJ22" s="22"/>
-      <c r="AK22" s="22"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="22"/>
+      <c r="AE22" s="24"/>
+      <c r="AI22" s="24"/>
       <c r="AR22" s="4"/>
       <c r="AS22" s="4"/>
     </row>
     <row r="23" spans="1:58" ht="12.75" customHeight="1">
       <c r="B23" s="3"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="22"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="22"/>
-      <c r="AK23" s="22"/>
-      <c r="AL23" s="22"/>
-      <c r="AM23" s="22"/>
       <c r="AR23" s="4"/>
       <c r="AS23" s="4"/>
     </row>
     <row r="24" spans="1:58" ht="12.75" customHeight="1">
       <c r="B24" s="3"/>
-      <c r="AD24" s="22"/>
-      <c r="AE24" s="26"/>
-      <c r="AF24" s="27"/>
-      <c r="AG24" s="28"/>
-      <c r="AH24" s="22"/>
-      <c r="AI24" s="26"/>
-      <c r="AJ24" s="27"/>
-      <c r="AK24" s="28"/>
-      <c r="AL24" s="26"/>
-      <c r="AM24" s="22"/>
+      <c r="AE24" s="10"/>
+      <c r="AF24" s="14"/>
+      <c r="AG24" s="25"/>
+      <c r="AI24" s="10"/>
+      <c r="AJ24" s="14"/>
+      <c r="AK24" s="25"/>
+      <c r="AL24" s="10"/>
       <c r="AR24" s="4"/>
       <c r="AS24" s="4"/>
     </row>
     <row r="25" spans="1:58" ht="12.75" customHeight="1">
       <c r="B25" s="3"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="26"/>
-      <c r="AF25" s="27"/>
-      <c r="AG25" s="28"/>
-      <c r="AH25" s="22"/>
-      <c r="AI25" s="26"/>
-      <c r="AJ25" s="27"/>
-      <c r="AK25" s="28"/>
-      <c r="AL25" s="26"/>
-      <c r="AM25" s="22"/>
+      <c r="AE25" s="10"/>
+      <c r="AF25" s="14"/>
+      <c r="AG25" s="25"/>
+      <c r="AI25" s="10"/>
+      <c r="AJ25" s="14"/>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="10"/>
       <c r="AR25" s="4"/>
       <c r="AS25" s="4"/>
     </row>
     <row r="26" spans="1:58">
-      <c r="AD26" s="22"/>
-      <c r="AE26" s="26"/>
-      <c r="AF26" s="27"/>
-      <c r="AG26" s="28"/>
-      <c r="AH26" s="22"/>
-      <c r="AI26" s="26"/>
-      <c r="AJ26" s="27"/>
-      <c r="AK26" s="28"/>
-      <c r="AL26" s="26"/>
-      <c r="AM26" s="22"/>
+      <c r="AE26" s="10"/>
+      <c r="AF26" s="14"/>
+      <c r="AG26" s="25"/>
+      <c r="AI26" s="10"/>
+      <c r="AJ26" s="14"/>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="10"/>
       <c r="AR26" s="4"/>
       <c r="AS26" s="4"/>
     </row>
     <row r="27" spans="1:58">
       <c r="C27" s="2"/>
-      <c r="AD27" s="22"/>
-      <c r="AE27" s="26"/>
-      <c r="AF27" s="27"/>
-      <c r="AG27" s="28"/>
-      <c r="AH27" s="22"/>
-      <c r="AI27" s="26"/>
-      <c r="AJ27" s="27"/>
-      <c r="AK27" s="28"/>
-      <c r="AL27" s="26"/>
-      <c r="AM27" s="22"/>
+      <c r="AE27" s="10"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="25"/>
+      <c r="AI27" s="10"/>
+      <c r="AJ27" s="14"/>
+      <c r="AK27" s="25"/>
+      <c r="AL27" s="10"/>
       <c r="AR27" s="4"/>
       <c r="AS27" s="4"/>
     </row>
     <row r="28" spans="1:58">
       <c r="C28" s="2"/>
-      <c r="AD28" s="22"/>
-      <c r="AE28" s="26"/>
-      <c r="AF28" s="27"/>
-      <c r="AG28" s="28"/>
-      <c r="AH28" s="22"/>
-      <c r="AI28" s="26"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="28"/>
-      <c r="AL28" s="26"/>
-      <c r="AM28" s="22"/>
+      <c r="AE28" s="10"/>
+      <c r="AF28" s="14"/>
+      <c r="AG28" s="25"/>
+      <c r="AI28" s="10"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="10"/>
       <c r="AR28" s="4"/>
       <c r="AS28" s="4"/>
     </row>
     <row r="29" spans="1:58">
       <c r="C29" s="2"/>
-      <c r="AD29" s="22"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="27"/>
-      <c r="AG29" s="28"/>
-      <c r="AH29" s="22"/>
-      <c r="AI29" s="26"/>
-      <c r="AJ29" s="27"/>
-      <c r="AK29" s="28"/>
-      <c r="AL29" s="26"/>
-      <c r="AM29" s="22"/>
+      <c r="AE29" s="10"/>
+      <c r="AF29" s="14"/>
+      <c r="AG29" s="25"/>
+      <c r="AI29" s="10"/>
+      <c r="AJ29" s="14"/>
+      <c r="AK29" s="25"/>
+      <c r="AL29" s="10"/>
       <c r="AR29" s="4"/>
       <c r="AS29" s="4"/>
     </row>
     <row r="30" spans="1:58">
       <c r="C30" s="2"/>
-      <c r="AD30" s="22"/>
-      <c r="AE30" s="26"/>
-      <c r="AF30" s="27"/>
-      <c r="AG30" s="28"/>
-      <c r="AH30" s="22"/>
-      <c r="AI30" s="26"/>
-      <c r="AJ30" s="27"/>
-      <c r="AK30" s="28"/>
-      <c r="AL30" s="26"/>
-      <c r="AM30" s="22"/>
+      <c r="AE30" s="10"/>
+      <c r="AF30" s="14"/>
+      <c r="AG30" s="25"/>
+      <c r="AI30" s="10"/>
+      <c r="AJ30" s="14"/>
+      <c r="AK30" s="25"/>
+      <c r="AL30" s="10"/>
       <c r="AR30" s="4"/>
       <c r="AS30" s="4"/>
     </row>
     <row r="31" spans="1:58">
       <c r="C31" s="2"/>
-      <c r="AD31" s="22"/>
-      <c r="AE31" s="26"/>
-      <c r="AF31" s="27"/>
-      <c r="AG31" s="28"/>
-      <c r="AH31" s="22"/>
-      <c r="AI31" s="26"/>
-      <c r="AJ31" s="27"/>
-      <c r="AK31" s="28"/>
-      <c r="AL31" s="26"/>
-      <c r="AM31" s="22"/>
+      <c r="AE31" s="10"/>
+      <c r="AF31" s="14"/>
+      <c r="AG31" s="25"/>
+      <c r="AI31" s="10"/>
+      <c r="AJ31" s="14"/>
+      <c r="AK31" s="25"/>
+      <c r="AL31" s="10"/>
       <c r="AR31" s="4"/>
       <c r="AS31" s="4"/>
     </row>
     <row r="32" spans="1:58">
       <c r="C32" s="2"/>
-      <c r="AD32" s="22"/>
-      <c r="AE32" s="26"/>
-      <c r="AF32" s="27"/>
-      <c r="AG32" s="28"/>
-      <c r="AH32" s="22"/>
-      <c r="AI32" s="26"/>
-      <c r="AJ32" s="27"/>
-      <c r="AK32" s="28"/>
-      <c r="AL32" s="26"/>
-      <c r="AM32" s="22"/>
+      <c r="AE32" s="10"/>
+      <c r="AF32" s="14"/>
+      <c r="AG32" s="25"/>
+      <c r="AI32" s="10"/>
+      <c r="AJ32" s="14"/>
+      <c r="AK32" s="25"/>
+      <c r="AL32" s="10"/>
       <c r="AR32" s="4"/>
       <c r="AS32" s="4"/>
     </row>
     <row r="33" spans="3:45">
       <c r="C33" s="2"/>
-      <c r="AD33" s="22"/>
-      <c r="AE33" s="26"/>
-      <c r="AF33" s="27"/>
-      <c r="AG33" s="28"/>
-      <c r="AH33" s="22"/>
-      <c r="AI33" s="26"/>
-      <c r="AJ33" s="27"/>
-      <c r="AK33" s="28"/>
-      <c r="AL33" s="26"/>
-      <c r="AM33" s="22"/>
+      <c r="AE33" s="10"/>
+      <c r="AF33" s="14"/>
+      <c r="AG33" s="25"/>
+      <c r="AI33" s="10"/>
+      <c r="AJ33" s="14"/>
+      <c r="AK33" s="25"/>
+      <c r="AL33" s="10"/>
       <c r="AR33" s="4"/>
       <c r="AS33" s="4"/>
     </row>
     <row r="34" spans="3:45">
       <c r="C34" s="2"/>
-      <c r="AD34" s="22"/>
-      <c r="AE34" s="26"/>
-      <c r="AF34" s="27"/>
-      <c r="AG34" s="28"/>
-      <c r="AH34" s="22"/>
-      <c r="AI34" s="26"/>
-      <c r="AJ34" s="27"/>
-      <c r="AK34" s="28"/>
-      <c r="AL34" s="26"/>
-      <c r="AM34" s="22"/>
+      <c r="AE34" s="10"/>
+      <c r="AF34" s="14"/>
+      <c r="AG34" s="25"/>
+      <c r="AI34" s="10"/>
+      <c r="AJ34" s="14"/>
+      <c r="AK34" s="25"/>
+      <c r="AL34" s="10"/>
       <c r="AR34" s="4"/>
       <c r="AS34" s="4"/>
     </row>
     <row r="35" spans="3:45">
       <c r="C35" s="2"/>
-      <c r="AD35" s="22"/>
-      <c r="AE35" s="26"/>
-      <c r="AF35" s="27"/>
-      <c r="AG35" s="28"/>
-      <c r="AH35" s="22"/>
-      <c r="AI35" s="26"/>
-      <c r="AJ35" s="27"/>
-      <c r="AK35" s="28"/>
-      <c r="AL35" s="26"/>
-      <c r="AM35" s="22"/>
+      <c r="AE35" s="10"/>
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="25"/>
+      <c r="AI35" s="10"/>
+      <c r="AJ35" s="14"/>
+      <c r="AK35" s="25"/>
+      <c r="AL35" s="10"/>
       <c r="AR35" s="4"/>
       <c r="AS35" s="4"/>
     </row>
     <row r="36" spans="3:45">
       <c r="C36" s="2"/>
-      <c r="AD36" s="22"/>
-      <c r="AE36" s="26"/>
-      <c r="AF36" s="27"/>
-      <c r="AG36" s="28"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="26"/>
-      <c r="AJ36" s="27"/>
-      <c r="AK36" s="28"/>
-      <c r="AL36" s="26"/>
-      <c r="AM36" s="22"/>
+      <c r="AE36" s="10"/>
+      <c r="AF36" s="14"/>
+      <c r="AG36" s="25"/>
+      <c r="AI36" s="10"/>
+      <c r="AJ36" s="14"/>
+      <c r="AK36" s="25"/>
+      <c r="AL36" s="10"/>
       <c r="AR36" s="4"/>
       <c r="AS36" s="4"/>
     </row>
     <row r="37" spans="3:45">
       <c r="C37" s="2"/>
-      <c r="AD37" s="22"/>
-      <c r="AE37" s="26"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="28"/>
-      <c r="AH37" s="22"/>
-      <c r="AI37" s="26"/>
-      <c r="AJ37" s="27"/>
-      <c r="AK37" s="28"/>
-      <c r="AL37" s="26"/>
-      <c r="AM37" s="22"/>
+      <c r="AE37" s="10"/>
+      <c r="AF37" s="14"/>
+      <c r="AG37" s="25"/>
+      <c r="AI37" s="10"/>
+      <c r="AJ37" s="14"/>
+      <c r="AK37" s="25"/>
+      <c r="AL37" s="10"/>
     </row>
     <row r="38" spans="3:45">
       <c r="C38" s="2"/>
-      <c r="AD38" s="22"/>
-      <c r="AE38" s="26"/>
-      <c r="AF38" s="27"/>
-      <c r="AG38" s="28"/>
-      <c r="AH38" s="22"/>
-      <c r="AI38" s="26"/>
-      <c r="AJ38" s="27"/>
-      <c r="AK38" s="28"/>
-      <c r="AL38" s="26"/>
-      <c r="AM38" s="22"/>
+      <c r="AE38" s="10"/>
+      <c r="AF38" s="14"/>
+      <c r="AG38" s="25"/>
+      <c r="AI38" s="10"/>
+      <c r="AJ38" s="14"/>
+      <c r="AK38" s="25"/>
+      <c r="AL38" s="10"/>
     </row>
     <row r="39" spans="3:45">
       <c r="C39" s="2"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="26"/>
-      <c r="AF39" s="27"/>
-      <c r="AG39" s="28"/>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="26"/>
-      <c r="AJ39" s="27"/>
-      <c r="AK39" s="28"/>
-      <c r="AL39" s="26"/>
-      <c r="AM39" s="22"/>
+      <c r="AE39" s="10"/>
+      <c r="AF39" s="14"/>
+      <c r="AG39" s="25"/>
+      <c r="AI39" s="10"/>
+      <c r="AJ39" s="14"/>
+      <c r="AK39" s="25"/>
+      <c r="AL39" s="10"/>
     </row>
     <row r="40" spans="3:45">
       <c r="C40" s="2"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-      <c r="AF40" s="22"/>
-      <c r="AG40" s="22"/>
-      <c r="AH40" s="22"/>
-      <c r="AI40" s="22"/>
-      <c r="AJ40" s="22"/>
-      <c r="AK40" s="22"/>
-      <c r="AL40" s="22"/>
-      <c r="AM40" s="22"/>
     </row>
     <row r="41" spans="3:45">
       <c r="C41" s="2"/>
-      <c r="AD41" s="22"/>
-      <c r="AE41" s="29"/>
-      <c r="AF41" s="29"/>
-      <c r="AG41" s="22"/>
-      <c r="AH41" s="22"/>
-      <c r="AI41" s="29"/>
-      <c r="AJ41" s="29"/>
-      <c r="AK41" s="22"/>
-      <c r="AL41" s="22"/>
-      <c r="AM41" s="22"/>
+      <c r="AE41" s="26"/>
+      <c r="AF41" s="26"/>
+      <c r="AI41" s="26"/>
+      <c r="AJ41" s="26"/>
     </row>
     <row r="42" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD42" s="22"/>
-      <c r="AE42" s="22"/>
-      <c r="AF42" s="22"/>
-      <c r="AG42" s="22"/>
-      <c r="AH42" s="22"/>
-      <c r="AI42" s="24"/>
-      <c r="AJ42" s="22"/>
-      <c r="AK42" s="22"/>
-      <c r="AL42" s="22"/>
-      <c r="AM42" s="22"/>
+      <c r="AI42" s="23"/>
     </row>
     <row r="43" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD43" s="22"/>
-      <c r="AE43" s="22"/>
-      <c r="AF43" s="22"/>
-      <c r="AG43" s="22"/>
-      <c r="AH43" s="22"/>
-      <c r="AI43" s="24"/>
-      <c r="AJ43" s="22"/>
-      <c r="AK43" s="22"/>
-      <c r="AL43" s="22"/>
-      <c r="AM43" s="22"/>
+      <c r="AI43" s="23"/>
     </row>
     <row r="44" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD44" s="22"/>
-      <c r="AE44" s="22"/>
-      <c r="AF44" s="22"/>
-      <c r="AG44" s="22"/>
-      <c r="AH44" s="22"/>
-      <c r="AI44" s="23"/>
-      <c r="AJ44" s="22"/>
-      <c r="AK44" s="22"/>
-      <c r="AL44" s="22"/>
-      <c r="AM44" s="22"/>
+      <c r="AI44" s="22"/>
     </row>
     <row r="45" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD45" s="22"/>
-      <c r="AE45" s="22"/>
-      <c r="AF45" s="22"/>
-      <c r="AG45" s="22"/>
-      <c r="AH45" s="22"/>
-      <c r="AI45" s="24"/>
-      <c r="AJ45" s="22"/>
-      <c r="AK45" s="22"/>
-      <c r="AL45" s="22"/>
-      <c r="AM45" s="22"/>
+      <c r="AI45" s="23"/>
     </row>
     <row r="46" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD46" s="22"/>
-      <c r="AE46" s="22"/>
-      <c r="AF46" s="22"/>
-      <c r="AG46" s="22"/>
-      <c r="AH46" s="22"/>
-      <c r="AI46" s="24"/>
-      <c r="AJ46" s="22"/>
-      <c r="AK46" s="22"/>
-      <c r="AL46" s="22"/>
-      <c r="AM46" s="22"/>
+      <c r="AI46" s="23"/>
     </row>
     <row r="47" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD47" s="22"/>
-      <c r="AE47" s="22"/>
-      <c r="AF47" s="22"/>
-      <c r="AG47" s="22"/>
-      <c r="AH47" s="22"/>
-      <c r="AI47" s="23"/>
-      <c r="AJ47" s="22"/>
-      <c r="AK47" s="22"/>
-      <c r="AL47" s="22"/>
-      <c r="AM47" s="22"/>
+      <c r="AI47" s="22"/>
     </row>
     <row r="48" spans="3:45" ht="12.75" customHeight="1">
-      <c r="AD48" s="22"/>
-      <c r="AE48" s="22"/>
-      <c r="AF48" s="22"/>
-      <c r="AG48" s="22"/>
-      <c r="AH48" s="22"/>
-      <c r="AI48" s="24"/>
-      <c r="AJ48" s="22"/>
-      <c r="AK48" s="22"/>
-      <c r="AL48" s="22"/>
-      <c r="AM48" s="22"/>
+      <c r="AI48" s="23"/>
     </row>
     <row r="49" spans="35:35" ht="12.75" customHeight="1">
       <c r="AI49" s="5"/>
@@ -4391,21 +4266,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20">
+      <c r="A1" s="27">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
@@ -4416,21 +4293,24 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
-      <c r="R1" t="s">
+      <c r="N1" s="10"/>
+      <c r="S1" t="s">
         <v>74</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="14.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:20" ht="14.25">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
@@ -4441,15 +4321,18 @@
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
-    </row>
-    <row r="3" spans="1:19" ht="14.25">
-      <c r="A3" t="s">
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="1:20" ht="14.25">
+      <c r="A3" s="27">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -4460,15 +4343,24 @@
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
-    </row>
-    <row r="4" spans="1:19" ht="14.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="N3" s="10"/>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="10"/>
+    </row>
+    <row r="4" spans="1:20" ht="14.25">
+      <c r="A4" s="27">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>79</v>
+      </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
@@ -4479,15 +4371,24 @@
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
-    </row>
-    <row r="5" spans="1:19" ht="14.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="14.25">
+      <c r="A5" s="27">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>81</v>
+      </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
@@ -4498,36 +4399,54 @@
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="14.25">
+      <c r="A6" s="28">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>83</v>
+      </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-    </row>
-    <row r="7" spans="1:19" ht="14.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="14.25">
+      <c r="A7" s="28">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>86</v>
+      </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -4538,15 +4457,24 @@
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="S7">
+        <v>5</v>
+      </c>
+      <c r="T7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="14.25">
+      <c r="A8" s="28">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>88</v>
+      </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -4557,15 +4485,24 @@
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="S8">
+        <v>6</v>
+      </c>
+      <c r="T8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="14.25">
+      <c r="A9" s="28">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>90</v>
+      </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -4576,36 +4513,54 @@
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="S9">
+        <v>7</v>
+      </c>
+      <c r="T9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="14.25">
+      <c r="A10" s="27">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>92</v>
+      </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
-    </row>
-    <row r="11" spans="1:19" ht="14.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="S10">
+        <v>8</v>
+      </c>
+      <c r="T10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="14.25">
+      <c r="A11" s="27">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -4616,15 +4571,24 @@
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
-    </row>
-    <row r="12" spans="1:19" ht="14.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="S11">
+        <v>9</v>
+      </c>
+      <c r="T11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="27">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>96</v>
+      </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -4635,15 +4599,24 @@
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="1:19" ht="14.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="S12">
+        <v>10</v>
+      </c>
+      <c r="T12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="27">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>98</v>
+      </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -4654,15 +4627,24 @@
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:19" ht="14.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="S13">
+        <v>11</v>
+      </c>
+      <c r="T13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="27">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>100</v>
+      </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -4673,15 +4655,18 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:19" ht="14.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="10"/>
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="27">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>101</v>
+      </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -4692,15 +4677,18 @@
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="10"/>
+      <c r="N15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="27">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -4711,15 +4699,18 @@
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
-    </row>
-    <row r="17" spans="1:13" ht="14.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="10"/>
+      <c r="N16" s="10"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="27">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>103</v>
+      </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -4730,15 +4721,18 @@
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:13" ht="14.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="10"/>
+      <c r="N17" s="10"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="27">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>104</v>
+      </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -4749,15 +4743,18 @@
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
-    </row>
-    <row r="19" spans="1:13" ht="14.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="10"/>
+      <c r="N18" s="10"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="27">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>105</v>
+      </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -4768,15 +4765,18 @@
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:13" ht="14.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="10"/>
+      <c r="N19" s="10"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="27">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>106</v>
+      </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -4787,15 +4787,18 @@
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
-    </row>
-    <row r="21" spans="1:13" ht="14.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="10"/>
+      <c r="N20" s="10"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="27">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>107</v>
+      </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -4806,15 +4809,18 @@
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="10"/>
+      <c r="N21" s="10"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="27">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>108</v>
+      </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -4825,15 +4831,18 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
-    </row>
-    <row r="23" spans="1:13" ht="14.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="10"/>
+      <c r="N22" s="10"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="27">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>109</v>
+      </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -4844,15 +4853,18 @@
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="10"/>
+      <c r="N23" s="10"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="27">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>110</v>
+      </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -4863,15 +4875,18 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="10"/>
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="27">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>111</v>
+      </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -4882,15 +4897,18 @@
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="10"/>
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="27">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>112</v>
+      </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -4901,15 +4919,18 @@
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="10"/>
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="27">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -4920,15 +4941,18 @@
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
-    </row>
-    <row r="28" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="10"/>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A28" s="27">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>114</v>
+      </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -4939,15 +4963,18 @@
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
-    </row>
-    <row r="29" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A29" t="s">
+      <c r="N28" s="10"/>
+    </row>
+    <row r="29" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A29" s="27">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="10" t="s">
+        <v>115</v>
+      </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -4958,17 +4985,20 @@
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
-    </row>
-    <row r="30" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A30" t="s">
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A30" s="27">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="14"/>
+      <c r="C30" s="14" t="s">
+        <v>116</v>
+      </c>
       <c r="D30" s="14"/>
-      <c r="E30" s="10"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -4977,15 +5007,18 @@
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
-    </row>
-    <row r="31" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A31" t="s">
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A31" s="27">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="10" t="s">
+        <v>117</v>
+      </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -4996,15 +5029,18 @@
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
       <c r="M31" s="10"/>
-    </row>
-    <row r="32" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="10"/>
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A32" s="27">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>118</v>
+      </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -5015,15 +5051,18 @@
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
       <c r="M32" s="10"/>
-    </row>
-    <row r="33" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="10"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A33" s="27">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>119</v>
+      </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -5034,15 +5073,18 @@
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
       <c r="M33" s="10"/>
-    </row>
-    <row r="34" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" s="10"/>
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A34" s="27">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>120</v>
+      </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -5053,15 +5095,18 @@
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="10"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="27">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>121</v>
+      </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -5072,15 +5117,18 @@
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
-    </row>
-    <row r="36" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="10"/>
+      <c r="N35" s="10"/>
+    </row>
+    <row r="36" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A36" s="27">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>122</v>
+      </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -5091,15 +5139,18 @@
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
-    </row>
-    <row r="37" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="10"/>
+      <c r="N36" s="10"/>
+    </row>
+    <row r="37" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A37" s="27">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>123</v>
+      </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -5110,15 +5161,18 @@
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
       <c r="M37" s="10"/>
-    </row>
-    <row r="38" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="10"/>
+      <c r="N37" s="10"/>
+    </row>
+    <row r="38" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A38" s="27">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>124</v>
+      </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
@@ -5129,15 +5183,18 @@
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
-    </row>
-    <row r="39" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="10"/>
+      <c r="N38" s="10"/>
+    </row>
+    <row r="39" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A39" s="27">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>125</v>
+      </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -5148,15 +5205,18 @@
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
-    </row>
-    <row r="40" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="10"/>
+      <c r="N39" s="10"/>
+    </row>
+    <row r="40" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A40" s="27">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -5167,15 +5227,18 @@
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
-    </row>
-    <row r="41" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="10"/>
+      <c r="N40" s="10"/>
+    </row>
+    <row r="41" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A41" s="27">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -5186,15 +5249,18 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-    </row>
-    <row r="42" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="10"/>
+      <c r="N41" s="10"/>
+    </row>
+    <row r="42" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A42" s="27">
+        <v>8</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>128</v>
+      </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -5205,15 +5271,18 @@
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
-    </row>
-    <row r="43" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="10"/>
+      <c r="N42" s="10"/>
+    </row>
+    <row r="43" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A43" s="27">
+        <v>8</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>129</v>
+      </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
@@ -5224,18 +5293,21 @@
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
       <c r="M43" s="10"/>
-    </row>
-    <row r="44" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="14"/>
+      <c r="N43" s="10"/>
+    </row>
+    <row r="44" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A44" s="27">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>130</v>
+      </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
-      <c r="F44" s="10"/>
+      <c r="F44" s="14"/>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
@@ -5243,15 +5315,18 @@
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
-    </row>
-    <row r="45" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="10"/>
+      <c r="N44" s="10"/>
+    </row>
+    <row r="45" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A45" s="27">
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>131</v>
+      </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
@@ -5262,15 +5337,18 @@
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
-    </row>
-    <row r="46" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="10"/>
+      <c r="N45" s="10"/>
+    </row>
+    <row r="46" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A46" s="27">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>132</v>
+      </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -5281,15 +5359,18 @@
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
       <c r="M46" s="10"/>
-    </row>
-    <row r="47" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C47" s="10"/>
+      <c r="N46" s="10"/>
+    </row>
+    <row r="47" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A47" s="27">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>133</v>
+      </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -5300,15 +5381,18 @@
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
-    </row>
-    <row r="48" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="10"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A48" s="27">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>134</v>
+      </c>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
@@ -5319,15 +5403,18 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
-    </row>
-    <row r="49" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C49" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A49" s="27">
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>135</v>
+      </c>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
@@ -5338,15 +5425,18 @@
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
-    </row>
-    <row r="50" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C50" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>136</v>
+      </c>
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
@@ -5357,15 +5447,18 @@
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
       <c r="M50" s="10"/>
-    </row>
-    <row r="51" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C51" s="10"/>
+      <c r="N50" s="10"/>
+    </row>
+    <row r="51" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A51" s="27">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>137</v>
+      </c>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
@@ -5376,15 +5469,18 @@
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
       <c r="M51" s="10"/>
-    </row>
-    <row r="52" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="10"/>
+      <c r="N51" s="10"/>
+    </row>
+    <row r="52" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A52" s="27">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>138</v>
+      </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
@@ -5395,15 +5491,18 @@
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
-    </row>
-    <row r="53" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C53" s="10"/>
+      <c r="N52" s="10"/>
+    </row>
+    <row r="53" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A53" s="27">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>139</v>
+      </c>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -5414,15 +5513,18 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
-    </row>
-    <row r="54" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" s="10"/>
+      <c r="N53" s="10"/>
+    </row>
+    <row r="54" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A54" s="27">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -5433,15 +5535,18 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10"/>
-    </row>
-    <row r="55" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="10"/>
+      <c r="N54" s="10"/>
+    </row>
+    <row r="55" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A55" s="27">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>141</v>
+      </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
@@ -5452,15 +5557,18 @@
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
-    </row>
-    <row r="56" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C56" s="10"/>
+      <c r="N55" s="10"/>
+    </row>
+    <row r="56" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A56" s="27">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>142</v>
+      </c>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -5471,15 +5579,18 @@
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
       <c r="M56" s="10"/>
-    </row>
-    <row r="57" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="10"/>
+      <c r="N56" s="10"/>
+    </row>
+    <row r="57" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A57" s="27">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>143</v>
+      </c>
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
@@ -5490,9 +5601,9 @@
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
       <c r="M57" s="10"/>
-    </row>
-    <row r="58" spans="1:13" ht="12.75" customHeight="1">
-      <c r="B58" s="10"/>
+      <c r="N57" s="10"/>
+    </row>
+    <row r="58" spans="1:14" ht="12.75" customHeight="1">
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
@@ -5504,9 +5615,9 @@
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
       <c r="M58" s="10"/>
-    </row>
-    <row r="59" spans="1:13" ht="12.75" customHeight="1">
-      <c r="B59" s="10"/>
+      <c r="N58" s="10"/>
+    </row>
+    <row r="59" spans="1:14" ht="12.75" customHeight="1">
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
@@ -5518,9 +5629,9 @@
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
       <c r="M59" s="10"/>
-    </row>
-    <row r="60" spans="1:13" ht="12.75" customHeight="1">
-      <c r="B60" s="10"/>
+      <c r="N59" s="10"/>
+    </row>
+    <row r="60" spans="1:14" ht="12.75" customHeight="1">
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="10"/>
@@ -5532,18 +5643,178 @@
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
       <c r="M60" s="10"/>
-    </row>
-    <row r="65" spans="1:1" ht="12.75" customHeight="1">
-      <c r="A65" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="12.75" customHeight="1">
-      <c r="A66" t="s">
-        <v>134</v>
+      <c r="N60" s="10"/>
+    </row>
+    <row r="65" spans="2:2" ht="12.75" customHeight="1">
+      <c r="B65" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="12.75" customHeight="1">
+      <c r="B66" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C57">
+    <sortCondition ref="A2:A57"/>
+  </sortState>
+  <conditionalFormatting sqref="A10:A19">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A29">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:A39">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40:A49">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50:A56">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:A9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A57">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A57">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -5563,7 +5834,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="226.5">
       <c r="A1" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/src/aw-dawid/Analiza wielowymiarowa.xlsx
+++ b/src/aw-dawid/Analiza wielowymiarowa.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="852" documentId="11_1CE57E2DD3C84F39559BD3B788AFFB502B3FCBC8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE6810C-F455-4117-9D65-9B0F608612B4}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dapha\Desktop\Repositories\poland-ab-mda\src\aw-dawid\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3FBBA9-88D5-490A-B31D-87020B61CB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dane zakodowane" sheetId="1" r:id="rId1"/>
@@ -14,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'dane zakodowane'!$AI$18:$AI$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'definicje zmiennych'!$A$2:$C$58</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="159">
   <si>
     <t>x1</t>
   </si>
@@ -307,6 +313,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> w 2024</t>
@@ -324,6 +332,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> w 2024</t>
@@ -341,6 +351,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> w 2024</t>
@@ -358,6 +370,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">i budzetów gmin I miast na prawach powiatu </t>
@@ -367,6 +381,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t>na Ochrona powietrza atmosferycznego i klimatu na 1 mieszkanca w 2024</t>
@@ -384,6 +400,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">i inwestycyjne budzetów gmin I miast na prawach powiatu </t>
@@ -393,6 +411,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t>na 1 mieszkanca w 2024</t>
@@ -518,6 +538,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Odsetek ludności w obiektach </t>
@@ -527,6 +549,8 @@
         <sz val="10"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> zbiorowego zakwaterowania</t>
@@ -536,6 +560,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 2021</t>
@@ -582,6 +608,42 @@
 Zespół pomieszczeń (pokoi i pomieszczeń pomocniczych) zlokalizowanych w jednym lub kilku budynkach, zajętych przez jeden odrębny zakład świadczący usługi: hotelarskie, opiekuńczo-wychowawcze, zdrowotne bądź inne usługi, które są związane z zamieszkaniem w takim zakładzie większej liczby osób, lub obiekt instytucji wyznaniowej, w szczególności dom parafialny, klasztor, dom zgromadzenia sióstr zakonnych.
 Dodatkowe wyjaśnienia metodologiczne:
 W niektórych obiektach (zakładach) osoby zamieszkują przez dłuższy czas (od kilku miesięcy do kilku lat) lub na stałe. Przykładowo takimi zakładami są: internaty, domy studenckie, hotele pracownicze, domy dziecka, domy opieki społecznej dla osób przewlekle chorych lub upośledzonych, klasztory, domy zakonne. Obiektami (zakładami), w których pobyt osób z reguły ma charakter krótkookresowy są m. in.: hotele, motele, domy wczasowe, pensjonaty, a także szpitale, sanatoria, prewentoria.</t>
+  </si>
+  <si>
+    <t>x01</t>
+  </si>
+  <si>
+    <t>x02</t>
+  </si>
+  <si>
+    <t>x03</t>
+  </si>
+  <si>
+    <t>x04</t>
+  </si>
+  <si>
+    <t>x05</t>
+  </si>
+  <si>
+    <t>x06</t>
+  </si>
+  <si>
+    <t>x07</t>
+  </si>
+  <si>
+    <t>x08</t>
+  </si>
+  <si>
+    <t>x09</t>
+  </si>
+  <si>
+    <t>grupa</t>
+  </si>
+  <si>
+    <t>zmienna</t>
+  </si>
+  <si>
+    <t>opis</t>
   </si>
 </sst>
 </file>
@@ -604,12 +666,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="8"/>
@@ -628,11 +692,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
@@ -649,55 +716,75 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.5"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="7" tint="0.39997558519241921"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -786,7 +873,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -818,7 +905,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1017,13 +1103,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BF49"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="35" max="35" width="12" bestFit="1" customWidth="1"/>
     <col min="41" max="42" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" ht="13.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1282,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:58" ht="15">
+    <row r="2" spans="1:58" ht="14.4">
       <c r="A2" s="1" t="s">
         <v>57</v>
       </c>
@@ -1372,7 +1458,7 @@
         <v>92027</v>
       </c>
     </row>
-    <row r="3" spans="1:58" ht="15">
+    <row r="3" spans="1:58" ht="14.4">
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
@@ -1548,7 +1634,7 @@
         <v>38307</v>
       </c>
     </row>
-    <row r="4" spans="1:58" ht="15">
+    <row r="4" spans="1:58" ht="14.4">
       <c r="A4" s="1" t="s">
         <v>59</v>
       </c>
@@ -1724,7 +1810,7 @@
         <v>19658</v>
       </c>
     </row>
-    <row r="5" spans="1:58" ht="15">
+    <row r="5" spans="1:58" ht="14.4">
       <c r="A5" s="1" t="s">
         <v>60</v>
       </c>
@@ -1900,7 +1986,7 @@
         <v>22775</v>
       </c>
     </row>
-    <row r="6" spans="1:58" ht="15">
+    <row r="6" spans="1:58" ht="14.4">
       <c r="A6" s="1" t="s">
         <v>61</v>
       </c>
@@ -2076,7 +2162,7 @@
         <v>68281</v>
       </c>
     </row>
-    <row r="7" spans="1:58" ht="15">
+    <row r="7" spans="1:58" ht="14.4">
       <c r="A7" s="1" t="s">
         <v>62</v>
       </c>
@@ -2252,7 +2338,7 @@
         <v>30064</v>
       </c>
     </row>
-    <row r="8" spans="1:58" ht="15">
+    <row r="8" spans="1:58" ht="14.4">
       <c r="A8" s="1" t="s">
         <v>63</v>
       </c>
@@ -2428,7 +2514,7 @@
         <v>120290</v>
       </c>
     </row>
-    <row r="9" spans="1:58" ht="15">
+    <row r="9" spans="1:58" ht="14.4">
       <c r="A9" s="1" t="s">
         <v>64</v>
       </c>
@@ -2604,7 +2690,7 @@
         <v>19570</v>
       </c>
     </row>
-    <row r="10" spans="1:58" ht="15">
+    <row r="10" spans="1:58" ht="14.4">
       <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
@@ -2780,7 +2866,7 @@
         <v>13762</v>
       </c>
     </row>
-    <row r="11" spans="1:58" ht="15">
+    <row r="11" spans="1:58" ht="14.4">
       <c r="A11" s="1" t="s">
         <v>66</v>
       </c>
@@ -2956,7 +3042,7 @@
         <v>13009</v>
       </c>
     </row>
-    <row r="12" spans="1:58" ht="15">
+    <row r="12" spans="1:58" ht="14.4">
       <c r="A12" s="1" t="s">
         <v>67</v>
       </c>
@@ -3132,7 +3218,7 @@
         <v>46931</v>
       </c>
     </row>
-    <row r="13" spans="1:58" ht="15">
+    <row r="13" spans="1:58" ht="14.4">
       <c r="A13" s="1" t="s">
         <v>68</v>
       </c>
@@ -3308,7 +3394,7 @@
         <v>147216</v>
       </c>
     </row>
-    <row r="14" spans="1:58" ht="15">
+    <row r="14" spans="1:58" ht="14.4">
       <c r="A14" s="1" t="s">
         <v>69</v>
       </c>
@@ -3484,7 +3570,7 @@
         <v>10559</v>
       </c>
     </row>
-    <row r="15" spans="1:58" ht="15">
+    <row r="15" spans="1:58" ht="14.4">
       <c r="A15" s="1" t="s">
         <v>70</v>
       </c>
@@ -3660,7 +3746,7 @@
         <v>23979</v>
       </c>
     </row>
-    <row r="16" spans="1:58" ht="15">
+    <row r="16" spans="1:58" ht="14.4">
       <c r="A16" s="1" t="s">
         <v>71</v>
       </c>
@@ -3836,7 +3922,7 @@
         <v>46662</v>
       </c>
     </row>
-    <row r="17" spans="1:58" ht="15">
+    <row r="17" spans="1:58" ht="14.4">
       <c r="A17" s="1" t="s">
         <v>72</v>
       </c>
@@ -4059,7 +4145,7 @@
       <c r="AR25" s="4"/>
       <c r="AS25" s="4"/>
     </row>
-    <row r="26" spans="1:58">
+    <row r="26" spans="1:58" ht="13.8">
       <c r="AE26" s="10"/>
       <c r="AF26" s="14"/>
       <c r="AG26" s="25"/>
@@ -4070,7 +4156,7 @@
       <c r="AR26" s="4"/>
       <c r="AS26" s="4"/>
     </row>
-    <row r="27" spans="1:58">
+    <row r="27" spans="1:58" ht="13.8">
       <c r="C27" s="2"/>
       <c r="AE27" s="10"/>
       <c r="AF27" s="14"/>
@@ -4082,7 +4168,7 @@
       <c r="AR27" s="4"/>
       <c r="AS27" s="4"/>
     </row>
-    <row r="28" spans="1:58">
+    <row r="28" spans="1:58" ht="13.8">
       <c r="C28" s="2"/>
       <c r="AE28" s="10"/>
       <c r="AF28" s="14"/>
@@ -4094,7 +4180,7 @@
       <c r="AR28" s="4"/>
       <c r="AS28" s="4"/>
     </row>
-    <row r="29" spans="1:58">
+    <row r="29" spans="1:58" ht="13.8">
       <c r="C29" s="2"/>
       <c r="AE29" s="10"/>
       <c r="AF29" s="14"/>
@@ -4106,7 +4192,7 @@
       <c r="AR29" s="4"/>
       <c r="AS29" s="4"/>
     </row>
-    <row r="30" spans="1:58">
+    <row r="30" spans="1:58" ht="13.8">
       <c r="C30" s="2"/>
       <c r="AE30" s="10"/>
       <c r="AF30" s="14"/>
@@ -4118,7 +4204,7 @@
       <c r="AR30" s="4"/>
       <c r="AS30" s="4"/>
     </row>
-    <row r="31" spans="1:58">
+    <row r="31" spans="1:58" ht="13.8">
       <c r="C31" s="2"/>
       <c r="AE31" s="10"/>
       <c r="AF31" s="14"/>
@@ -4130,7 +4216,7 @@
       <c r="AR31" s="4"/>
       <c r="AS31" s="4"/>
     </row>
-    <row r="32" spans="1:58">
+    <row r="32" spans="1:58" ht="13.8">
       <c r="C32" s="2"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="14"/>
@@ -4142,7 +4228,7 @@
       <c r="AR32" s="4"/>
       <c r="AS32" s="4"/>
     </row>
-    <row r="33" spans="3:45">
+    <row r="33" spans="3:45" ht="13.8">
       <c r="C33" s="2"/>
       <c r="AE33" s="10"/>
       <c r="AF33" s="14"/>
@@ -4154,7 +4240,7 @@
       <c r="AR33" s="4"/>
       <c r="AS33" s="4"/>
     </row>
-    <row r="34" spans="3:45">
+    <row r="34" spans="3:45" ht="13.8">
       <c r="C34" s="2"/>
       <c r="AE34" s="10"/>
       <c r="AF34" s="14"/>
@@ -4166,7 +4252,7 @@
       <c r="AR34" s="4"/>
       <c r="AS34" s="4"/>
     </row>
-    <row r="35" spans="3:45">
+    <row r="35" spans="3:45" ht="13.8">
       <c r="C35" s="2"/>
       <c r="AE35" s="10"/>
       <c r="AF35" s="14"/>
@@ -4178,7 +4264,7 @@
       <c r="AR35" s="4"/>
       <c r="AS35" s="4"/>
     </row>
-    <row r="36" spans="3:45">
+    <row r="36" spans="3:45" ht="13.8">
       <c r="C36" s="2"/>
       <c r="AE36" s="10"/>
       <c r="AF36" s="14"/>
@@ -4190,7 +4276,7 @@
       <c r="AR36" s="4"/>
       <c r="AS36" s="4"/>
     </row>
-    <row r="37" spans="3:45">
+    <row r="37" spans="3:45" ht="13.2">
       <c r="C37" s="2"/>
       <c r="AE37" s="10"/>
       <c r="AF37" s="14"/>
@@ -4200,7 +4286,7 @@
       <c r="AK37" s="25"/>
       <c r="AL37" s="10"/>
     </row>
-    <row r="38" spans="3:45">
+    <row r="38" spans="3:45" ht="13.2">
       <c r="C38" s="2"/>
       <c r="AE38" s="10"/>
       <c r="AF38" s="14"/>
@@ -4210,7 +4296,7 @@
       <c r="AK38" s="25"/>
       <c r="AL38" s="10"/>
     </row>
-    <row r="39" spans="3:45">
+    <row r="39" spans="3:45" ht="13.2">
       <c r="C39" s="2"/>
       <c r="AE39" s="10"/>
       <c r="AF39" s="14"/>
@@ -4220,10 +4306,10 @@
       <c r="AK39" s="25"/>
       <c r="AL39" s="10"/>
     </row>
-    <row r="40" spans="3:45">
+    <row r="40" spans="3:45" ht="13.2">
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="3:45">
+    <row r="41" spans="3:45" ht="13.2">
       <c r="C41" s="2"/>
       <c r="AE41" s="26"/>
       <c r="AF41" s="26"/>
@@ -4266,50 +4352,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T66"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:T67"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="17" max="17" width="11.42578125" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.44140625" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="27">
+    <row r="1" spans="1:20" ht="12.75" customHeight="1">
+      <c r="A1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="13.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="S1" t="s">
-        <v>74</v>
-      </c>
-      <c r="T1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="14.25">
-      <c r="A2" s="27">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>76</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -4322,16 +4391,22 @@
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
-    </row>
-    <row r="3" spans="1:20" ht="14.25">
-      <c r="A3" s="27">
-        <v>1</v>
+      <c r="S2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="13.2">
+      <c r="A3">
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>77</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -4344,22 +4419,16 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="14.25">
+    </row>
+    <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>79</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -4373,21 +4442,21 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="13.8">
+      <c r="A5" s="27">
         <v>2</v>
       </c>
-      <c r="T4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="14.25">
-      <c r="A5" s="27">
-        <v>1</v>
-      </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>81</v>
+        <v>11</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -4401,21 +4470,21 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
       <c r="S5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="14.25">
-      <c r="A6" s="28">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="13.8">
+      <c r="A6" s="27">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>83</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -4423,29 +4492,27 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="10" t="s">
-        <v>84</v>
-      </c>
+      <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="S6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="14.25">
-      <c r="A7" s="28">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="13.8">
+      <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>86</v>
+        <v>13</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -4453,27 +4520,29 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
       <c r="S7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="14.25">
-      <c r="A8" s="28">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="13.8">
+      <c r="A8">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>88</v>
+        <v>14</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>94</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -4487,21 +4556,21 @@
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
       <c r="S8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="14.25">
-      <c r="A9" s="28">
-        <v>2</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="13.2">
+      <c r="A9">
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -4515,21 +4584,21 @@
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="S9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="14.25">
-      <c r="A10" s="27">
-        <v>2</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="13.8">
+      <c r="A10">
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -4537,29 +4606,27 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
-      <c r="J10" s="10" t="s">
-        <v>84</v>
-      </c>
+      <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="S10">
+        <v>7</v>
+      </c>
+      <c r="T10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="13.8">
+      <c r="A11">
         <v>8</v>
       </c>
-      <c r="T10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="14.25">
-      <c r="A11" s="27">
-        <v>2</v>
-      </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -4567,27 +4634,29 @@
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
+      <c r="J11" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
       <c r="S11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="27">
-        <v>3</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="13.8">
+      <c r="A12">
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>96</v>
+        <v>18</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>128</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -4601,21 +4670,21 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="S12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="27">
-        <v>3</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="13.8">
+      <c r="A13">
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>98</v>
+        <v>148</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -4629,21 +4698,21 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
       <c r="S13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="27">
-        <v>3</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="13.8">
+      <c r="A14">
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>100</v>
+        <v>19</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -4656,16 +4725,22 @@
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="27">
-        <v>3</v>
+      <c r="S14">
+        <v>11</v>
+      </c>
+      <c r="T14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="13.8">
+      <c r="A15">
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>101</v>
+        <v>20</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>130</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -4679,15 +4754,15 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="27">
-        <v>3</v>
+    <row r="16" spans="1:20" ht="13.2">
+      <c r="A16">
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -4701,15 +4776,15 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="27">
-        <v>3</v>
+    <row r="17" spans="1:14" ht="13.8">
+      <c r="A17">
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>122</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -4723,15 +4798,15 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="27">
-        <v>3</v>
+    <row r="18" spans="1:14" ht="13.2">
+      <c r="A18">
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>123</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -4745,15 +4820,15 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="27">
-        <v>3</v>
+    <row r="19" spans="1:14" ht="13.2">
+      <c r="A19">
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>105</v>
+        <v>24</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -4767,15 +4842,15 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="27">
-        <v>3</v>
+    <row r="20" spans="1:14" ht="13.2">
+      <c r="A20">
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>106</v>
+        <v>25</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -4789,15 +4864,15 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="27">
-        <v>3</v>
+    <row r="21" spans="1:14" ht="13.2">
+      <c r="A21">
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -4811,15 +4886,15 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="27">
-        <v>3</v>
+    <row r="22" spans="1:14" ht="13.2">
+      <c r="A22">
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>108</v>
+        <v>27</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
@@ -4833,15 +4908,15 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="27">
-        <v>4</v>
+    <row r="23" spans="1:14" ht="13.2">
+      <c r="A23">
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -4855,15 +4930,15 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="27">
-        <v>4</v>
+    <row r="24" spans="1:14" ht="13.8">
+      <c r="A24">
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>110</v>
+        <v>149</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -4877,15 +4952,15 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="27">
-        <v>4</v>
+    <row r="25" spans="1:14" ht="13.2">
+      <c r="A25">
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>111</v>
+        <v>29</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
@@ -4899,15 +4974,15 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="27">
-        <v>4</v>
+    <row r="26" spans="1:14" ht="13.2">
+      <c r="A26">
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -4921,15 +4996,15 @@
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="27">
-        <v>5</v>
+    <row r="27" spans="1:14" ht="13.2">
+      <c r="A27">
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -4943,15 +5018,15 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A28" s="27">
-        <v>5</v>
+    <row r="28" spans="1:14" ht="13.2">
+      <c r="A28">
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>114</v>
+        <v>32</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -4966,14 +5041,14 @@
       <c r="N28" s="10"/>
     </row>
     <row r="29" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A29" s="27">
+      <c r="A29">
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -4988,17 +5063,17 @@
       <c r="N29" s="10"/>
     </row>
     <row r="30" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A30" s="27">
+      <c r="A30">
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -5010,17 +5085,17 @@
       <c r="N30" s="10"/>
     </row>
     <row r="31" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A31" s="27">
-        <v>6</v>
+      <c r="A31">
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+        <v>35</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -5032,14 +5107,14 @@
       <c r="N31" s="10"/>
     </row>
     <row r="32" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A32" s="27">
-        <v>6</v>
+      <c r="A32">
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
@@ -5054,14 +5129,14 @@
       <c r="N32" s="10"/>
     </row>
     <row r="33" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A33" s="27">
+      <c r="A33">
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -5076,14 +5151,14 @@
       <c r="N33" s="10"/>
     </row>
     <row r="34" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A34" s="27">
+      <c r="A34">
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -5097,15 +5172,15 @@
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" ht="12.75" customHeight="1">
       <c r="A35" s="27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>121</v>
+        <v>150</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -5119,15 +5194,15 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A36" s="27">
-        <v>7</v>
+    <row r="36" spans="1:14" ht="13.2">
+      <c r="A36">
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>122</v>
+        <v>39</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
@@ -5142,14 +5217,14 @@
       <c r="N36" s="10"/>
     </row>
     <row r="37" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A37" s="27">
-        <v>7</v>
+      <c r="A37">
+        <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>123</v>
+        <v>40</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -5164,14 +5239,14 @@
       <c r="N37" s="10"/>
     </row>
     <row r="38" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A38" s="27">
-        <v>7</v>
+      <c r="A38">
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>124</v>
+        <v>41</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
@@ -5186,14 +5261,14 @@
       <c r="N38" s="10"/>
     </row>
     <row r="39" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A39" s="27">
-        <v>7</v>
+      <c r="A39">
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -5208,14 +5283,14 @@
       <c r="N39" s="10"/>
     </row>
     <row r="40" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A40" s="27">
-        <v>7</v>
+      <c r="A40">
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>126</v>
+        <v>43</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>143</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -5230,14 +5305,14 @@
       <c r="N40" s="10"/>
     </row>
     <row r="41" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A41" s="27">
-        <v>8</v>
+      <c r="A41">
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>127</v>
+        <v>44</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
@@ -5252,14 +5327,14 @@
       <c r="N41" s="10"/>
     </row>
     <row r="42" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A42" s="27">
-        <v>8</v>
+      <c r="A42">
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>128</v>
+        <v>45</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -5274,14 +5349,14 @@
       <c r="N42" s="10"/>
     </row>
     <row r="43" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A43" s="27">
-        <v>8</v>
+      <c r="A43">
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>129</v>
+        <v>46</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -5296,18 +5371,18 @@
       <c r="N43" s="10"/>
     </row>
     <row r="44" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A44" s="27">
-        <v>8</v>
+      <c r="A44">
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
@@ -5318,18 +5393,18 @@
       <c r="N44" s="10"/>
     </row>
     <row r="45" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A45" s="27">
-        <v>8</v>
+      <c r="A45">
+        <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
@@ -5340,14 +5415,14 @@
       <c r="N45" s="10"/>
     </row>
     <row r="46" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A46" s="27">
-        <v>9</v>
+      <c r="A46">
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>132</v>
+        <v>151</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
@@ -5362,14 +5437,14 @@
       <c r="N46" s="10"/>
     </row>
     <row r="47" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A47" s="27">
-        <v>9</v>
+      <c r="A47">
+        <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>133</v>
+        <v>49</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
@@ -5384,14 +5459,14 @@
       <c r="N47" s="10"/>
     </row>
     <row r="48" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A48" s="27">
-        <v>9</v>
+      <c r="A48">
+        <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>134</v>
+        <v>50</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
@@ -5406,14 +5481,14 @@
       <c r="N48" s="10"/>
     </row>
     <row r="49" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A49" s="27">
-        <v>9</v>
+      <c r="A49">
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
@@ -5429,13 +5504,13 @@
     </row>
     <row r="50" spans="1:14" ht="12.75" customHeight="1">
       <c r="A50">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>136</v>
+        <v>52</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
@@ -5450,14 +5525,14 @@
       <c r="N50" s="10"/>
     </row>
     <row r="51" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A51" s="27">
-        <v>10</v>
+      <c r="A51">
+        <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
@@ -5472,14 +5547,14 @@
       <c r="N51" s="10"/>
     </row>
     <row r="52" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A52" s="27">
-        <v>10</v>
+      <c r="A52">
+        <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>138</v>
+        <v>54</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>106</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
@@ -5494,14 +5569,14 @@
       <c r="N52" s="10"/>
     </row>
     <row r="53" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A53" s="27">
-        <v>11</v>
+      <c r="A53">
+        <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>139</v>
+        <v>55</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
@@ -5516,14 +5591,14 @@
       <c r="N53" s="10"/>
     </row>
     <row r="54" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A54" s="27">
-        <v>11</v>
+      <c r="A54">
+        <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
@@ -5538,14 +5613,14 @@
       <c r="N54" s="10"/>
     </row>
     <row r="55" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A55" s="27">
-        <v>11</v>
+      <c r="A55">
+        <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
@@ -5560,14 +5635,14 @@
       <c r="N55" s="10"/>
     </row>
     <row r="56" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A56" s="27">
-        <v>11</v>
+      <c r="A56">
+        <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>142</v>
+        <v>153</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
@@ -5582,14 +5657,14 @@
       <c r="N56" s="10"/>
     </row>
     <row r="57" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A57" s="27">
-        <v>11</v>
+      <c r="A57">
+        <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>143</v>
+        <v>154</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
@@ -5604,7 +5679,15 @@
       <c r="N57" s="10"/>
     </row>
     <row r="58" spans="1:14" ht="12.75" customHeight="1">
-      <c r="C58" s="10"/>
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>114</v>
+      </c>
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
@@ -5645,22 +5728,37 @@
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
     </row>
-    <row r="65" spans="2:2" ht="12.75" customHeight="1">
-      <c r="B65" t="s">
-        <v>144</v>
-      </c>
+    <row r="61" spans="1:14" ht="12.75" customHeight="1">
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
     </row>
     <row r="66" spans="2:2" ht="12.75" customHeight="1">
       <c r="B66" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="12.75" customHeight="1">
+      <c r="B67" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C57">
-    <sortCondition ref="A2:A57"/>
+  <autoFilter ref="A2:C58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C58">
+    <sortCondition ref="A3:A58"/>
   </sortState>
-  <conditionalFormatting sqref="A10:A19">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="A2">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5671,8 +5769,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:A29">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="A2:A58">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5683,55 +5791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A30:A39">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A40:A49">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50:A56">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:A9">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
+  <conditionalFormatting sqref="A3">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5744,7 +5804,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5755,8 +5815,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="A5">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5767,8 +5827,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="A6">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5779,8 +5839,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="A7:A10">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5791,7 +5851,77 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A57">
+  <conditionalFormatting sqref="A11:A20">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A30">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A40">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:A50">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51:A57">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O55:O58">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5803,15 +5933,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A57">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="O55:O57">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -5827,12 +5957,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9326C97B-652B-474C-BDFB-BD9105DC5E51}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="55.5703125" customWidth="1"/>
+    <col min="1" max="1" width="55.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="226.5">
+    <row r="1" spans="1:1" ht="250.8">
       <c r="A1" s="6" t="s">
         <v>146</v>
       </c>

--- a/src/aw-dawid/Analiza wielowymiarowa.xlsx
+++ b/src/aw-dawid/Analiza wielowymiarowa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dapha\Desktop\Repositories\poland-ab-mda\src\aw-dawid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3FBBA9-88D5-490A-B31D-87020B61CB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FAB06C-00AE-4F5C-8067-B1542EED0CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'dane zakodowane'!$AI$18:$AI$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'definicje zmiennych'!$A$2:$C$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'definicje zmiennych'!$A$1:$C$58</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -4398,15 +4398,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="13.2">
+    <row r="3" spans="1:20" ht="13.8">
       <c r="A3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>132</v>
+        <v>148</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -4421,14 +4421,14 @@
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
-      <c r="A4" s="27">
-        <v>2</v>
+      <c r="A4">
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>86</v>
+        <v>149</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -4453,10 +4453,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>88</v>
+        <v>150</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -4477,14 +4477,14 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="13.8">
-      <c r="A6" s="27">
-        <v>2</v>
+      <c r="A6">
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>90</v>
+        <v>151</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -4504,15 +4504,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="13.8">
+    <row r="7" spans="1:20" ht="13.2">
       <c r="A7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>92</v>
+        <v>152</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -4536,13 +4536,13 @@
     </row>
     <row r="8" spans="1:20" ht="13.8">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>94</v>
+        <v>153</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -4564,13 +4564,13 @@
     </row>
     <row r="9" spans="1:20" ht="13.2">
       <c r="A9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -4590,15 +4590,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="13.8">
+    <row r="10" spans="1:20" ht="13.2">
       <c r="A10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>138</v>
+        <v>155</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -4618,15 +4618,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="13.8">
+    <row r="11" spans="1:20" ht="13.2">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>127</v>
+        <v>9</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -4649,14 +4649,14 @@
       </c>
     </row>
     <row r="12" spans="1:20" ht="13.8">
-      <c r="A12">
-        <v>8</v>
+      <c r="A12" s="27">
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>128</v>
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -4677,14 +4677,14 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="13.8">
-      <c r="A13">
-        <v>1</v>
+      <c r="A13" s="27">
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>76</v>
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -4705,14 +4705,14 @@
       </c>
     </row>
     <row r="14" spans="1:20" ht="13.8">
-      <c r="A14">
-        <v>8</v>
+      <c r="A14" s="27">
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>129</v>
+        <v>12</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -4734,13 +4734,13 @@
     </row>
     <row r="15" spans="1:20" ht="13.8">
       <c r="A15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -4754,15 +4754,15 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:20" ht="13.2">
+    <row r="16" spans="1:20" ht="13.8">
       <c r="A16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>131</v>
+        <v>14</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>94</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -4776,15 +4776,15 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="13.8">
+    <row r="17" spans="1:14" ht="13.2">
       <c r="A17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>122</v>
+        <v>15</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -4798,15 +4798,15 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="13.2">
+    <row r="18" spans="1:14" ht="13.8">
       <c r="A18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>123</v>
+        <v>16</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -4820,15 +4820,15 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="13.2">
+    <row r="19" spans="1:14" ht="13.8">
       <c r="A19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>124</v>
+        <v>17</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>127</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -4842,15 +4842,15 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="13.2">
+    <row r="20" spans="1:14" ht="13.8">
       <c r="A20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>125</v>
+        <v>18</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>128</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -4864,15 +4864,15 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="13.2">
+    <row r="21" spans="1:14" ht="13.8">
       <c r="A21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>126</v>
+        <v>19</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -4886,15 +4886,15 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="13.2">
+    <row r="22" spans="1:14" ht="13.8">
       <c r="A22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>140</v>
+        <v>20</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>130</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
@@ -4910,13 +4910,13 @@
     </row>
     <row r="23" spans="1:14" ht="13.2">
       <c r="A23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -4932,13 +4932,13 @@
     </row>
     <row r="24" spans="1:14" ht="13.8">
       <c r="A24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>77</v>
+        <v>22</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>122</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -4954,13 +4954,13 @@
     </row>
     <row r="25" spans="1:14" ht="13.2">
       <c r="A25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>116</v>
+        <v>23</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>123</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
@@ -4976,13 +4976,13 @@
     </row>
     <row r="26" spans="1:14" ht="13.2">
       <c r="A26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>117</v>
+        <v>24</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -4998,13 +4998,13 @@
     </row>
     <row r="27" spans="1:14" ht="13.2">
       <c r="A27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -5020,13 +5020,13 @@
     </row>
     <row r="28" spans="1:14" ht="13.2">
       <c r="A28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -5042,13 +5042,13 @@
     </row>
     <row r="29" spans="1:14" ht="12.75" customHeight="1">
       <c r="A29">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -5067,10 +5067,10 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
@@ -5086,13 +5086,13 @@
     </row>
     <row r="31" spans="1:14" ht="12.75" customHeight="1">
       <c r="A31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>133</v>
+        <v>29</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
@@ -5108,13 +5108,13 @@
     </row>
     <row r="32" spans="1:14" ht="12.75" customHeight="1">
       <c r="A32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
@@ -5130,13 +5130,13 @@
     </row>
     <row r="33" spans="1:14" ht="12.75" customHeight="1">
       <c r="A33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -5152,13 +5152,13 @@
     </row>
     <row r="34" spans="1:14" ht="12.75" customHeight="1">
       <c r="A34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -5173,14 +5173,14 @@
       <c r="N34" s="10"/>
     </row>
     <row r="35" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A35" s="27">
-        <v>2</v>
+      <c r="A35">
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>83</v>
+        <v>33</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -5196,13 +5196,13 @@
     </row>
     <row r="36" spans="1:14" ht="13.2">
       <c r="A36">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
@@ -5221,10 +5221,10 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>134</v>
+        <v>35</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>133</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -5240,13 +5240,13 @@
     </row>
     <row r="38" spans="1:14" ht="12.75" customHeight="1">
       <c r="A38">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
@@ -5262,13 +5262,13 @@
     </row>
     <row r="39" spans="1:14" ht="12.75" customHeight="1">
       <c r="A39">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -5284,13 +5284,13 @@
     </row>
     <row r="40" spans="1:14" ht="12.75" customHeight="1">
       <c r="A40">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>143</v>
+        <v>38</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -5309,10 +5309,10 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
@@ -5328,13 +5328,13 @@
     </row>
     <row r="42" spans="1:14" ht="12.75" customHeight="1">
       <c r="A42">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>96</v>
+        <v>40</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -5350,13 +5350,13 @@
     </row>
     <row r="43" spans="1:14" ht="12.75" customHeight="1">
       <c r="A43">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -5372,13 +5372,13 @@
     </row>
     <row r="44" spans="1:14" ht="12.75" customHeight="1">
       <c r="A44">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>100</v>
+        <v>42</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>142</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
@@ -5394,13 +5394,13 @@
     </row>
     <row r="45" spans="1:14" ht="12.75" customHeight="1">
       <c r="A45">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>101</v>
+        <v>43</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>143</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
@@ -5416,13 +5416,13 @@
     </row>
     <row r="46" spans="1:14" ht="12.75" customHeight="1">
       <c r="A46">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>79</v>
+        <v>44</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
@@ -5441,10 +5441,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
@@ -5463,10 +5463,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
@@ -5485,10 +5485,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>104</v>
+        <v>47</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
@@ -5507,10 +5507,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
@@ -5529,10 +5529,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
@@ -5551,10 +5551,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>106</v>
+        <v>50</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
@@ -5573,10 +5573,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>108</v>
+        <v>51</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
@@ -5592,13 +5592,13 @@
     </row>
     <row r="54" spans="1:14" ht="12.75" customHeight="1">
       <c r="A54">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>136</v>
+        <v>52</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
@@ -5614,13 +5614,13 @@
     </row>
     <row r="55" spans="1:14" ht="12.75" customHeight="1">
       <c r="A55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
@@ -5636,13 +5636,13 @@
     </row>
     <row r="56" spans="1:14" ht="12.75" customHeight="1">
       <c r="A56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>81</v>
+        <v>54</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>106</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="57" spans="1:14" ht="12.75" customHeight="1">
       <c r="A57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>109</v>
+        <v>55</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
@@ -5680,13 +5680,13 @@
     </row>
     <row r="58" spans="1:14" ht="12.75" customHeight="1">
       <c r="A58">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>114</v>
+        <v>56</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
@@ -5753,7 +5753,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:C58" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C58">
+      <sortCondition ref="B1:B58"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C58">
     <sortCondition ref="A3:A58"/>
   </sortState>
@@ -5911,6 +5915,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O55:O57">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="O55:O58">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -5923,18 +5939,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O55:O57">
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
